--- a/MapBiome_地图主题表.xlsx
+++ b/MapBiome_地图主题表.xlsx
@@ -7,11 +7,132 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapBiomeSheet0" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapBiomeSheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+  <si>
+    <t>类名</t>
+  </si>
+  <si>
+    <t>MapBiome_地图主题表</t>
+  </si>
+  <si>
+    <t>是否读取</t>
+  </si>
+  <si>
+    <t>IsConfig</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>美术/瓦片主题 Key（与 TileMap 目录名一致）</t>
+  </si>
+  <si>
+    <t>中文名</t>
+  </si>
+  <si>
+    <t>空间层：1 地下 2 地表 3 地表建筑</t>
+  </si>
+  <si>
+    <t>整图重生成上限</t>
+  </si>
+  <si>
+    <t>是否启用</t>
+  </si>
+  <si>
+    <t>敌人生命倍率</t>
+  </si>
+  <si>
+    <t>敌人伤害倍率</t>
+  </si>
+  <si>
+    <t>掉落组基号</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>themeKey</t>
+  </si>
+  <si>
+    <t>nameCN</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>retryMax</t>
+  </si>
+  <si>
+    <t>enable</t>
+  </si>
+  <si>
+    <t>EnemyHpMul</t>
+  </si>
+  <si>
+    <t>EnemyDmgMul</t>
+  </si>
+  <si>
+    <t>DropGroupBase</t>
+  </si>
+  <si>
+    <t>client</t>
+  </si>
+  <si>
+    <t>uint</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>Underground</t>
+  </si>
+  <si>
+    <t>地下</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>地表</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>地表建筑</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,16 +140,16 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,10 +168,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,248 +534,230 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>类名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MapBiome_地图主题表</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>是否读取</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IsConfig</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>美术/瓦片主题 Key（与 TileMap 目录名一致）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>中文名</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>空间层：1 地下 2 地表 3 地表建筑</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>整图重生成上限</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>是否启用</t>
-        </is>
+      <c r="A3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>themeKey</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>nameCN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>layer</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>retryMax</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>enable</t>
-        </is>
+      <c r="A4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>client</t>
-        </is>
+      <c r="A5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>uint</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>uint</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>uint</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
+      <c r="A6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="0">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Underground</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>地下</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="0">
         <v>1</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0">
         <v>20</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="F7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="0">
         <v>2</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Surface</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>地表</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="0">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0">
         <v>20</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="F8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="0">
         <v>3</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Building</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>地表建筑</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="0">
         <v>3</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0">
         <v>20</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="F9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>